--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mismatches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,10 @@
     <font>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
@@ -57,22 +62,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,14 +115,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,12 +502,12 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="78" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,7 +538,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Why</t>
+          <t>Why / note</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -552,7 +563,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Their purpose</t>
+          <t>Their stated purpose</t>
         </is>
       </c>
     </row>
@@ -622,7 +633,7 @@
           <t>marketing.segment</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>DECLINE</t>
         </is>
@@ -669,7 +680,7 @@
           <t>sync.rejection</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>DECLINE</t>
         </is>
@@ -716,10 +727,14 @@
           <t>ai.policy</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>ours is richer, 26 columns against their 17</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -759,10 +774,14 @@
           <t>approvals.decision</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -802,10 +821,14 @@
           <t>approvals.delegation</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -852,7 +875,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ours is a 2-column stub</t>
+          <t>ours is a 2-column stub; keep our name, take their columns</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -892,10 +915,14 @@
           <t>approvals.matrix</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -935,10 +962,14 @@
           <t>approvals.request</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -978,10 +1009,14 @@
           <t>approvals.rule</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -1021,10 +1056,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>pairs with variant_dimension; 11 inbound FKs</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -1064,10 +1103,14 @@
           <t>fnb.table</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>dining_ disambiguates; fnb.table alone is vague next to reservation_table</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -1107,14 +1150,14 @@
           <t>fnb.table</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>a join table mapping tables to a reservation, not a second name for fnb.table</t>
+          <t>maps tables to a reservation; a join table we do not have</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
@@ -1154,10 +1197,14 @@
           <t>inventory.count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
@@ -1197,10 +1244,14 @@
           <t>inventory.count_line</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
@@ -1236,10 +1287,14 @@
           <t>inventory.movement</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
@@ -1279,10 +1334,14 @@
           <t>inventory.transfer</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -1322,10 +1381,14 @@
           <t>inventory.transfer_line</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
@@ -1361,10 +1424,14 @@
           <t>marketing.challenge_progress</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -1404,14 +1471,14 @@
           <t>marketing.campaign</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>links a campaign to loyalty bonuses; a different table</t>
+          <t>links a campaign to loyalty bonuses; a different table, not a rename</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
@@ -1451,10 +1518,14 @@
           <t>marketing.case</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>ours already means support cases only</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
@@ -1541,10 +1612,14 @@
           <t>platform.denomination</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>cash_ is meaningful but we hold no other denomination; concede if useful</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -1584,10 +1659,14 @@
           <t>reporting.execution</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
@@ -1627,10 +1706,14 @@
           <t>reporting.schedule</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -1670,10 +1753,14 @@
           <t>resources.booking</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
@@ -1713,10 +1800,14 @@
           <t>seating.section_row</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>their table-name prefix; our exact table exists</t>
+          <t>the table name repeats its schema; same habit as the 645 column renames</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
@@ -1737,7 +1828,7 @@
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>domain-move</t>
         </is>
@@ -1752,10 +1843,14 @@
           <t>accreditation.credential</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>same table, we put the domain in its own schema</t>
+          <t>we give the domain its own schema; same principle they accepted for branding-&gt;whitelabel</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
@@ -1780,7 +1875,7 @@
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>domain-move</t>
         </is>
@@ -1795,10 +1890,14 @@
           <t>accreditation.document</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>same table, we put the domain in its own schema</t>
+          <t>we give the domain its own schema; same principle they accepted for branding-&gt;whitelabel</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
@@ -1823,7 +1922,7 @@
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>domain-move</t>
         </is>
@@ -1838,10 +1937,14 @@
           <t>rental.damage_assessment</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>same table, we put the domain in its own schema</t>
+          <t>we give the domain its own schema; same principle they accepted for branding-&gt;whitelabel</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -1866,7 +1969,7 @@
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>domain-move</t>
         </is>
@@ -1881,10 +1984,14 @@
           <t>rental.inspection</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>same table, we put the domain in its own schema</t>
+          <t>we give the domain its own schema; same principle they accepted for branding-&gt;whitelabel</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -1909,7 +2016,7 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -1924,14 +2031,14 @@
           <t>catalogue.price</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
@@ -1956,7 +2063,7 @@
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -1971,14 +2078,14 @@
           <t>catalogue.price_list</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
@@ -2003,7 +2110,7 @@
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2018,14 +2125,14 @@
           <t>catalogue.product</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -2050,7 +2157,7 @@
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2065,14 +2172,14 @@
           <t>catalogue.product_category</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
@@ -2097,7 +2204,7 @@
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2112,14 +2219,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G37" s="2" t="n">
@@ -2144,7 +2251,7 @@
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2159,7 +2266,7 @@
           <t>approvals.sla_policy</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
@@ -2191,7 +2298,7 @@
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2206,7 +2313,7 @@
           <t>ledger.deposit</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
@@ -2238,7 +2345,7 @@
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2253,10 +2360,14 @@
           <t>control.cell</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>same table name, different owning schema</t>
+          <t>ours is in control with 20 columns and 19 inbound FKs</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -2281,7 +2392,7 @@
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2296,14 +2407,14 @@
           <t>catalogue.price</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -2328,7 +2439,7 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2343,14 +2454,14 @@
           <t>catalogue.price_list</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -2375,7 +2486,7 @@
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2390,14 +2501,14 @@
           <t>catalogue.product</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G43" s="2" t="n">
@@ -2422,7 +2533,7 @@
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2437,14 +2548,14 @@
           <t>catalogue.product_category</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
@@ -2469,7 +2580,7 @@
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2484,14 +2595,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>F&amp;B/Retail stand alone by decision; their purpose says it does not depend on Catalogue</t>
+          <t>F&amp;B/Retail stand alone; their purpose says it does not depend on Catalogue</t>
         </is>
       </c>
       <c r="G45" s="2" t="n">
@@ -2516,7 +2627,7 @@
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2531,10 +2642,14 @@
           <t>platform.guest_link</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>same table name, different owning schema</t>
+          <t>which schema owns cross-cell guest linking, sync or platform</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
@@ -2557,7 +2672,7 @@
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2572,14 +2687,14 @@
           <t>platform.outlet</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>the venue schema question — still an open blocker</t>
+          <t>the venue schema question — an open blocker</t>
         </is>
       </c>
       <c r="G47" s="2" t="n">
@@ -2604,7 +2719,7 @@
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2619,14 +2734,14 @@
           <t>catalogue.space</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>the venue schema question — still an open blocker</t>
+          <t>the venue schema question — an open blocker</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
@@ -2651,7 +2766,7 @@
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2666,14 +2781,14 @@
           <t>seating.zone</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>the venue schema question — still an open blocker</t>
+          <t>the venue schema question — an open blocker</t>
         </is>
       </c>
       <c r="G49" s="2" t="n">
@@ -2698,7 +2813,7 @@
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2713,7 +2828,7 @@
           <t>ledger.account</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>RECLASSIFY</t>
         </is>
@@ -2745,7 +2860,7 @@
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2760,7 +2875,7 @@
           <t>fnb.menu_item</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>RECLASSIFY</t>
         </is>
@@ -2792,7 +2907,7 @@
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2807,7 +2922,7 @@
           <t>orders.shift</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>ADDITIVE</t>
         </is>
@@ -2839,7 +2954,7 @@
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -2882,7 +2997,7 @@
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -2925,7 +3040,7 @@
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -2968,7 +3083,7 @@
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3011,7 +3126,7 @@
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3054,7 +3169,7 @@
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3097,7 +3212,7 @@
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3140,7 +3255,7 @@
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3183,7 +3298,7 @@
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3226,7 +3341,7 @@
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3265,7 +3380,7 @@
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3308,7 +3423,7 @@
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3355,7 +3470,7 @@
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3398,7 +3513,7 @@
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3441,7 +3556,7 @@
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3456,10 +3571,14 @@
           <t>platform.region_settings</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.73</t>
+          <t>singular vs plural only; settle our own convention first</t>
         </is>
       </c>
       <c r="G67" s="2" t="n">
@@ -3484,7 +3603,7 @@
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3527,7 +3646,7 @@
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3570,7 +3689,7 @@
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3611,7 +3730,7 @@
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
@@ -3654,7 +3773,7 @@
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3697,7 +3816,7 @@
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3740,7 +3859,7 @@
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3783,7 +3902,7 @@
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3826,7 +3945,7 @@
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3869,7 +3988,7 @@
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3912,7 +4031,7 @@
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3951,7 +4070,7 @@
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -3990,7 +4109,7 @@
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4033,7 +4152,7 @@
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4076,7 +4195,7 @@
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4117,7 +4236,7 @@
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4160,7 +4279,7 @@
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4203,7 +4322,7 @@
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4246,7 +4365,7 @@
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4289,7 +4408,7 @@
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4332,7 +4451,7 @@
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4375,7 +4494,7 @@
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4418,7 +4537,7 @@
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4461,7 +4580,7 @@
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4504,7 +4623,7 @@
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4545,7 +4664,7 @@
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4586,7 +4705,7 @@
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4629,7 +4748,7 @@
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4672,7 +4791,7 @@
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4715,7 +4834,7 @@
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4758,7 +4877,7 @@
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4801,7 +4920,7 @@
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4840,7 +4959,7 @@
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
@@ -4883,7 +5002,7 @@
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -4926,7 +5045,7 @@
       <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B102" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -4969,7 +5088,7 @@
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B103" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5012,7 +5131,7 @@
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5055,7 +5174,7 @@
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5098,7 +5217,7 @@
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5141,7 +5260,7 @@
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5184,7 +5303,7 @@
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5227,7 +5346,7 @@
       <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5270,7 +5389,7 @@
       <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5313,7 +5432,7 @@
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="9" t="inlineStr">
+      <c r="B111" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5352,7 +5471,7 @@
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="9" t="inlineStr">
+      <c r="B112" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5395,7 +5514,7 @@
       <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5438,7 +5557,7 @@
       <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5477,7 +5596,7 @@
       <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B115" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5520,7 +5639,7 @@
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5563,7 +5682,7 @@
       <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5606,7 +5725,7 @@
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5645,7 +5764,7 @@
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5688,7 +5807,7 @@
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B120" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5727,7 +5846,7 @@
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="9" t="inlineStr">
+      <c r="B121" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5770,7 +5889,7 @@
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="9" t="inlineStr">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5813,7 +5932,7 @@
       <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B123" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5856,7 +5975,7 @@
       <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5899,7 +6018,7 @@
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B125" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5942,7 +6061,7 @@
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -5981,7 +6100,7 @@
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6020,7 +6139,7 @@
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B128" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6059,7 +6178,7 @@
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="9" t="inlineStr">
+      <c r="B129" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6098,7 +6217,7 @@
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B130" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6137,7 +6256,7 @@
       <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="9" t="inlineStr">
+      <c r="B131" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6176,7 +6295,7 @@
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B132" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6219,7 +6338,7 @@
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="9" t="inlineStr">
+      <c r="B133" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6262,7 +6381,7 @@
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="9" t="inlineStr">
+      <c r="B134" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6305,7 +6424,7 @@
       <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B135" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6348,7 +6467,7 @@
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B136" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6391,7 +6510,7 @@
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="9" t="inlineStr">
+      <c r="B137" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6430,7 +6549,7 @@
       <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6469,7 +6588,7 @@
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="9" t="inlineStr">
+      <c r="B139" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6512,7 +6631,7 @@
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B140" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6555,7 +6674,7 @@
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B141" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6598,7 +6717,7 @@
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="9" t="inlineStr">
+      <c r="B142" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6641,7 +6760,7 @@
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6684,7 +6803,7 @@
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B144" s="13" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
@@ -6727,7 +6846,7 @@
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="10" t="inlineStr">
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6758,7 +6877,7 @@
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="10" t="inlineStr">
+      <c r="B146" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6789,7 +6908,7 @@
       <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B147" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6820,7 +6939,7 @@
       <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="10" t="inlineStr">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6851,7 +6970,7 @@
       <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6882,7 +7001,7 @@
       <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="10" t="inlineStr">
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6913,7 +7032,7 @@
       <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="10" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6944,7 +7063,7 @@
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="10" t="inlineStr">
+      <c r="B152" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -6975,7 +7094,7 @@
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="10" t="inlineStr">
+      <c r="B153" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -7006,7 +7125,7 @@
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="10" t="inlineStr">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -7037,7 +7156,7 @@
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="10" t="inlineStr">
+      <c r="B155" s="14" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
@@ -7068,7 +7187,7 @@
       <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="10" t="inlineStr">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7099,7 +7218,7 @@
       <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B157" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7130,7 +7249,7 @@
       <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="10" t="inlineStr">
+      <c r="B158" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7161,7 +7280,7 @@
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="10" t="inlineStr">
+      <c r="B159" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7192,7 +7311,7 @@
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="10" t="inlineStr">
+      <c r="B160" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7223,7 +7342,7 @@
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="10" t="inlineStr">
+      <c r="B161" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7254,7 +7373,7 @@
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="10" t="inlineStr">
+      <c r="B162" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7285,7 +7404,7 @@
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B163" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7316,7 +7435,7 @@
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="10" t="inlineStr">
+      <c r="B164" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7347,7 +7466,7 @@
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="10" t="inlineStr">
+      <c r="B165" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7378,7 +7497,7 @@
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="10" t="inlineStr">
+      <c r="B166" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7409,7 +7528,7 @@
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="10" t="inlineStr">
+      <c r="B167" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7440,7 +7559,7 @@
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="10" t="inlineStr">
+      <c r="B168" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7471,7 +7590,7 @@
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="10" t="inlineStr">
+      <c r="B169" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7502,7 +7621,7 @@
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="10" t="inlineStr">
+      <c r="B170" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7533,7 +7652,7 @@
       <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="10" t="inlineStr">
+      <c r="B171" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7564,7 +7683,7 @@
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="10" t="inlineStr">
+      <c r="B172" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7595,7 +7714,7 @@
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="10" t="inlineStr">
+      <c r="B173" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7626,7 +7745,7 @@
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B174" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7657,7 +7776,7 @@
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="10" t="inlineStr">
+      <c r="B175" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7688,7 +7807,7 @@
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B176" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7719,7 +7838,7 @@
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B177" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7750,7 +7869,7 @@
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="10" t="inlineStr">
+      <c r="B178" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7781,7 +7900,7 @@
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="10" t="inlineStr">
+      <c r="B179" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7812,7 +7931,7 @@
       <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="10" t="inlineStr">
+      <c r="B180" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7843,7 +7962,7 @@
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="10" t="inlineStr">
+      <c r="B181" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7874,7 +7993,7 @@
       <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="10" t="inlineStr">
+      <c r="B182" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7905,7 +8024,7 @@
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="10" t="inlineStr">
+      <c r="B183" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7936,7 +8055,7 @@
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="10" t="inlineStr">
+      <c r="B184" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7967,7 +8086,7 @@
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="10" t="inlineStr">
+      <c r="B185" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -7998,7 +8117,7 @@
       <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="10" t="inlineStr">
+      <c r="B186" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8029,7 +8148,7 @@
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="10" t="inlineStr">
+      <c r="B187" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8060,7 +8179,7 @@
       <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="10" t="inlineStr">
+      <c r="B188" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8091,7 +8210,7 @@
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="10" t="inlineStr">
+      <c r="B189" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8122,7 +8241,7 @@
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="10" t="inlineStr">
+      <c r="B190" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8153,7 +8272,7 @@
       <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="10" t="inlineStr">
+      <c r="B191" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8184,7 +8303,7 @@
       <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="10" t="inlineStr">
+      <c r="B192" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8215,7 +8334,7 @@
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="10" t="inlineStr">
+      <c r="B193" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8246,7 +8365,7 @@
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="10" t="inlineStr">
+      <c r="B194" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8277,7 +8396,7 @@
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="10" t="inlineStr">
+      <c r="B195" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8308,7 +8427,7 @@
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="10" t="inlineStr">
+      <c r="B196" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8339,7 +8458,7 @@
       <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B197" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8370,7 +8489,7 @@
       <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B198" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8401,7 +8520,7 @@
       <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="10" t="inlineStr">
+      <c r="B199" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8432,7 +8551,7 @@
       <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="10" t="inlineStr">
+      <c r="B200" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8463,7 +8582,7 @@
       <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="10" t="inlineStr">
+      <c r="B201" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8494,7 +8613,7 @@
       <c r="A202" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B202" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8525,7 +8644,7 @@
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="10" t="inlineStr">
+      <c r="B203" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8556,7 +8675,7 @@
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="10" t="inlineStr">
+      <c r="B204" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8587,7 +8706,7 @@
       <c r="A205" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="10" t="inlineStr">
+      <c r="B205" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8618,7 +8737,7 @@
       <c r="A206" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B206" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8649,7 +8768,7 @@
       <c r="A207" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="10" t="inlineStr">
+      <c r="B207" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8680,7 +8799,7 @@
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="10" t="inlineStr">
+      <c r="B208" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8711,7 +8830,7 @@
       <c r="A209" s="2" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="10" t="inlineStr">
+      <c r="B209" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8742,7 +8861,7 @@
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="10" t="inlineStr">
+      <c r="B210" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8773,7 +8892,7 @@
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="10" t="inlineStr">
+      <c r="B211" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8804,7 +8923,7 @@
       <c r="A212" s="2" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="10" t="inlineStr">
+      <c r="B212" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8835,7 +8954,7 @@
       <c r="A213" s="2" t="n">
         <v>212</v>
       </c>
-      <c r="B213" s="10" t="inlineStr">
+      <c r="B213" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8866,7 +8985,7 @@
       <c r="A214" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="B214" s="10" t="inlineStr">
+      <c r="B214" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8897,7 +9016,7 @@
       <c r="A215" s="2" t="n">
         <v>214</v>
       </c>
-      <c r="B215" s="10" t="inlineStr">
+      <c r="B215" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8928,7 +9047,7 @@
       <c r="A216" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="B216" s="10" t="inlineStr">
+      <c r="B216" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8959,7 +9078,7 @@
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
-      <c r="B217" s="10" t="inlineStr">
+      <c r="B217" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -8990,7 +9109,7 @@
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
-      <c r="B218" s="10" t="inlineStr">
+      <c r="B218" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9021,7 +9140,7 @@
       <c r="A219" s="2" t="n">
         <v>218</v>
       </c>
-      <c r="B219" s="10" t="inlineStr">
+      <c r="B219" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9052,7 +9171,7 @@
       <c r="A220" s="2" t="n">
         <v>219</v>
       </c>
-      <c r="B220" s="10" t="inlineStr">
+      <c r="B220" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9083,7 +9202,7 @@
       <c r="A221" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="B221" s="10" t="inlineStr">
+      <c r="B221" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9114,7 +9233,7 @@
       <c r="A222" s="2" t="n">
         <v>221</v>
       </c>
-      <c r="B222" s="10" t="inlineStr">
+      <c r="B222" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9145,7 +9264,7 @@
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="B223" s="10" t="inlineStr">
+      <c r="B223" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9176,7 +9295,7 @@
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
-      <c r="B224" s="10" t="inlineStr">
+      <c r="B224" s="14" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
@@ -9206,4 +9325,171 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>TICVAI schema merge — 223 of their tables that share no name with ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>53 decided, 170 open. Verdicts in handoff/merge-verdicts.json; regenerate with the same script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>rename-declared</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>rename-certain</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>domain-move</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>placement</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>rename-strong</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>rename-review</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>rename-ambiguous</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>additive-declared</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -107,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +132,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +506,7 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
@@ -528,7 +532,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Our table</t>
+          <t>Our candidate</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -3788,10 +3792,14 @@
           <t>ai.knowledge_collection</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>TAKE EITHER</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>their "searchable knowledge base" is our knowledge_collection; a vocabulary choice</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -3831,10 +3839,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>matched catalogue.variant on noise; upsell lives in promotions for us</t>
         </is>
       </c>
       <c r="G73" s="2" t="n">
@@ -3874,10 +3886,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>rental domain; ours is rental.pricing_profile</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
@@ -3917,10 +3933,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>rental domain; ours is rental.agreement_rules</t>
         </is>
       </c>
       <c r="G75" s="2" t="n">
@@ -3960,10 +3980,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>rental domain; ours is rental.operational_rules</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
@@ -4003,10 +4027,14 @@
           <t>catalogue.variant</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>matched catalogue.variant on noise; we serve upgrades by operation, not a rule table</t>
         </is>
       </c>
       <c r="G77" s="2" t="n">
@@ -4046,10 +4074,14 @@
           <t>control.cell_instance</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>matched cell_instance on noise; a sales-channel table needs its own check</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
@@ -4085,10 +4117,14 @@
           <t>control.cell_instance</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>matched cell_instance on noise; channel-to-item mapping</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
@@ -4124,10 +4160,14 @@
           <t>identity.principal</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>customer extra-field choices; we have no extensible profile fields</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
@@ -4167,10 +4207,14 @@
           <t>identity.delegated_access</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.45</t>
+          <t>module enablement per tenant — ours is whitelabel.module_enablement</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -4210,10 +4254,14 @@
           <t>identity.access_override</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>we hold session but no refresh-token rotation record</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
@@ -4251,10 +4299,14 @@
           <t>identity.delegated_access</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.54</t>
+          <t>assigns a role to a principal in a scope — we have role_permission and delegated_access but no grant table</t>
         </is>
       </c>
       <c r="G83" s="2" t="n">
@@ -4294,10 +4346,14 @@
           <t>identity.principal</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.44</t>
+          <t>principal is ours and covers person, service and device, which their own purpose describes</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
@@ -4337,10 +4393,14 @@
           <t>ledger.journal_entry</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.56</t>
+          <t>their journal is the header; ours is journal_entry with journal_line beneath it</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
@@ -4380,10 +4440,14 @@
           <t>marketing.segment_criterion</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>segment_criterion is ours and customer_ repeats the schema</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -4423,10 +4487,14 @@
           <t>marketing.journey_entrant</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>enrollment is the clearer word; journey_entrant reads as a person, not a state</t>
         </is>
       </c>
       <c r="G87" s="2" t="n">
@@ -4466,10 +4534,14 @@
           <t>marketing.loyalty_programme</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>we hold journey and journey_entrant and no steps</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
@@ -4509,10 +4581,14 @@
           <t>marketing.loyalty_programme</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>SPLIT</t>
+        </is>
+      </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>they split earning and redemption; our loyalty_programme holds both</t>
         </is>
       </c>
       <c r="G89" s="2" t="n">
@@ -4552,10 +4628,14 @@
           <t>marketing.loyalty_programme</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>SPLIT</t>
+        </is>
+      </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>they split earning and redemption; our loyalty_programme holds both</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
@@ -4595,10 +4675,14 @@
           <t>marketing.loyalty_programme</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.57</t>
+          <t>we hold loyalty_programme, _tier and _position but no reward</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
@@ -4638,10 +4722,14 @@
           <t>orders.fraud_rule</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>payments domain; ours is payments.provider_connection</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
@@ -4679,10 +4767,14 @@
           <t>orders.fraud_rule</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>payments domain; ours is payments.method</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
@@ -4720,10 +4812,14 @@
           <t>orders.reservation</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>payments domain; ours is payments.payment_terms</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
@@ -4763,10 +4859,14 @@
           <t>orders.reservation</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>payments domain; ours is payments.terminal</t>
         </is>
       </c>
       <c r="G95" s="2" t="n">
@@ -4806,10 +4906,14 @@
           <t>platform.dsar_request</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>how one cell reaches another; we have no endpoint record</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
@@ -4849,10 +4953,14 @@
           <t>platform.dsar_request</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>subscription domain; ours is control.subscription</t>
         </is>
       </c>
       <c r="G97" s="2" t="n">
@@ -4892,10 +5000,14 @@
           <t>reporting.report_parameter</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.43</t>
+          <t>parameter is the domain word</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
@@ -4935,10 +5047,14 @@
           <t>resources.resource_relation</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.50</t>
+          <t>rental domain; ours is rental.equipment_assignment</t>
         </is>
       </c>
       <c r="G99" s="2" t="n">
@@ -4974,10 +5090,14 @@
           <t>whitelabel.config_version</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>one candidate, containment 0.40</t>
+          <t>config_version vs brand_version; concede, it costs nothing</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
@@ -9333,25 +9453,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>TICVAI schema merge — 223 of their tables that share no name with ours</t>
+          <t>TICVAI schema merge — 223 tables of theirs that share no name with ours</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>53 decided, 170 open. Verdicts in handoff/merge-verdicts.json; regenerate with the same script.</t>
+          <t>82 decided, 141 open. Verdicts live in handoff/merge-verdicts.json; this sheet is generated from them.</t>
         </is>
       </c>
     </row>
@@ -9371,6 +9495,21 @@
           <t>Decided</t>
         </is>
       </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -9384,6 +9523,17 @@
       <c r="C5" s="16" t="n">
         <v>3</v>
       </c>
+      <c r="D5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -9397,6 +9547,17 @@
       <c r="C6" s="16" t="n">
         <v>24</v>
       </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -9410,6 +9571,17 @@
       <c r="C7" s="16" t="n">
         <v>4</v>
       </c>
+      <c r="D7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -9423,6 +9595,17 @@
       <c r="C8" s="16" t="n">
         <v>20</v>
       </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -9436,6 +9619,17 @@
       <c r="C9" s="16" t="n">
         <v>2</v>
       </c>
+      <c r="D9" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -9447,7 +9641,18 @@
         <v>29</v>
       </c>
       <c r="C10" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="D10" s="16" t="n">
         <v>0</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -9462,6 +9667,17 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D11" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -9475,6 +9691,17 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -9487,6 +9714,71 @@
       </c>
       <c r="C13" s="16" t="n">
         <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>TAKE BODY</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>SPLIT</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>RECLASSIFY</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>TAKE EITHER</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,9 +41,6 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -110,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -132,7 +129,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7318,10 +7314,14 @@
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr"/>
-      <c r="E156" s="4" t="inlineStr"/>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>audits access replacement during an upgrade</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
@@ -7349,10 +7349,14 @@
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr"/>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our accreditation.holder</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
@@ -7380,10 +7384,14 @@
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our accreditation.holder_access</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
@@ -7411,10 +7419,14 @@
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr"/>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our accreditation.audit</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
@@ -7442,10 +7454,14 @@
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>KEEP OURS</t>
+        </is>
+      </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our accreditation.programme</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
@@ -7473,10 +7489,14 @@
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr"/>
-      <c r="E161" s="4" t="inlineStr"/>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>join between admission_rules and access_point; we imply it and never store it</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
@@ -7504,10 +7524,14 @@
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr"/>
-      <c r="E162" s="4" t="inlineStr"/>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>maps benefits to a plan with usage limits</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
@@ -7535,10 +7559,14 @@
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr"/>
+      <c r="E163" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>approved substitutions for a recipe</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr"/>
@@ -7566,10 +7594,14 @@
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr"/>
-      <c r="E164" s="4" t="inlineStr"/>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>join between menu_item and modifier group</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
@@ -7597,10 +7629,14 @@
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr"/>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>F&amp;B upsell; ours lives in promotions and not per product</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
@@ -7628,10 +7664,14 @@
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr"/>
-      <c r="E166" s="4" t="inlineStr"/>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>use of a membership benefit against its allowance</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
@@ -7659,10 +7699,14 @@
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr"/>
-      <c r="E167" s="4" t="inlineStr"/>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>a guest is marketing.guest_profile plus pii.subject; identity holds principals</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
@@ -7690,10 +7734,14 @@
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="4" t="inlineStr"/>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>pii.subject_contact holds guest contact detail</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
@@ -7721,10 +7769,14 @@
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr"/>
-      <c r="E169" s="4" t="inlineStr"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our pii.subject_contact</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
@@ -7752,10 +7804,14 @@
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr"/>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the membership a customer holds; we have entitlement_template and no holder record</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
@@ -7783,10 +7839,14 @@
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr"/>
-      <c r="E171" s="4" t="inlineStr"/>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our marketing.guest_relationship</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
@@ -7814,10 +7874,14 @@
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr"/>
-      <c r="E172" s="4" t="inlineStr"/>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our marketing.guest_relationship</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
@@ -7845,10 +7909,14 @@
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr"/>
-      <c r="E173" s="4" t="inlineStr"/>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>status history for a membership</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
@@ -7876,10 +7944,14 @@
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr"/>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>a registry of authorisation modules; ours live in contracts/shared/permissions.yaml, not a table</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
@@ -7907,10 +7979,14 @@
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr"/>
-      <c r="E175" s="4" t="inlineStr"/>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>same — the permission vocabulary is a contract file for us, not data</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
@@ -7938,10 +8014,14 @@
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr"/>
-      <c r="E176" s="4" t="inlineStr"/>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our identity.principal_credential</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
@@ -7969,10 +8049,14 @@
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr"/>
-      <c r="E177" s="4" t="inlineStr"/>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>purchasing agreement and terms with a supplier</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr"/>
@@ -8000,10 +8084,14 @@
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr"/>
-      <c r="E178" s="4" t="inlineStr"/>
+      <c r="E178" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>links a campaign to what it promotes</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
@@ -8031,10 +8119,14 @@
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our marketing.case_message</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
@@ -8062,10 +8154,14 @@
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr"/>
-      <c r="E180" s="4" t="inlineStr"/>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>badges awarded; we have challenge and challenge_progress and no badge</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
@@ -8093,10 +8189,14 @@
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr"/>
-      <c r="E181" s="4" t="inlineStr"/>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>PLACEMENT</t>
+        </is>
+      </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>duplicates our platform.dsar_request — flagged 18 September, still true</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
@@ -8124,10 +8224,14 @@
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr"/>
-      <c r="E182" s="4" t="inlineStr"/>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the points ledger; we hold loyalty_position and no transaction history</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
@@ -8155,10 +8259,14 @@
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr"/>
-      <c r="E183" s="4" t="inlineStr"/>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>SPLIT</t>
+        </is>
+      </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>their earning and bonus rules; ours sit inside loyalty_programme</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
@@ -8186,10 +8294,14 @@
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr"/>
+      <c r="E184" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>staff replies to a review; we hold review alone</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
@@ -8217,10 +8329,14 @@
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr"/>
+      <c r="E185" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>which reward went to whom; pairs with marketing.reward</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
@@ -8248,10 +8364,14 @@
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr"/>
-      <c r="E186" s="4" t="inlineStr"/>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our marketing.form_definition covers surveys and waivers as one shape</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
@@ -8279,10 +8399,14 @@
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our marketing.form_submission</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr"/>
@@ -8310,10 +8434,14 @@
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr"/>
-      <c r="E188" s="4" t="inlineStr"/>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>signature against an immutable waiver version; form_submission does not pin the version</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
@@ -8341,10 +8469,14 @@
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr"/>
-      <c r="E189" s="4" t="inlineStr"/>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>ours rolls cash_count_line up to the shift; theirs is the session header</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
@@ -8372,10 +8504,14 @@
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr"/>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>renewal attempts and their result</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
@@ -8403,10 +8539,14 @@
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr"/>
-      <c r="E191" s="4" t="inlineStr"/>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>COLLISION</t>
+        </is>
+      </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payments domain; ours is payments.routing_rule</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
@@ -8434,10 +8574,14 @@
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr"/>
-      <c r="E192" s="4" t="inlineStr"/>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our platform.configuration_profile is scope-addressed</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
@@ -8465,10 +8609,14 @@
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr"/>
-      <c r="E193" s="4" t="inlineStr"/>
+      <c r="E193" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr"/>
@@ -8496,10 +8644,14 @@
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr"/>
-      <c r="E194" s="4" t="inlineStr"/>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr"/>
@@ -8527,10 +8679,14 @@
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr"/>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr"/>
@@ -8558,10 +8714,14 @@
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr"/>
-      <c r="E196" s="4" t="inlineStr"/>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>retail upsell, same shape</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr"/>
@@ -8589,10 +8749,14 @@
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr"/>
-      <c r="E197" s="4" t="inlineStr"/>
+      <c r="E197" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the seats inside a hold; we hold seat_hold and hold_pool only</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr"/>
@@ -8620,10 +8784,14 @@
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr"/>
-      <c r="E198" s="4" t="inlineStr"/>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>which cell may talk to which; we have no permit record</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr"/>
@@ -8651,10 +8819,14 @@
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="4" t="inlineStr"/>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the request itself; we hold only sync.rejection</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr"/>
@@ -8682,10 +8854,14 @@
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr"/>
-      <c r="E200" s="4" t="inlineStr"/>
+      <c r="E200" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the venue schema question, with outlet, space and zone</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr"/>
@@ -8713,10 +8889,14 @@
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr"/>
+      <c r="E201" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>the venue schema question, with outlet, space and zone</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr"/>
@@ -8744,10 +8924,14 @@
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr"/>
-      <c r="E202" s="4" t="inlineStr"/>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our venuemap.map</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr"/>
@@ -8775,10 +8959,14 @@
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="4" t="inlineStr"/>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our wallet.shared_wallet_member says who may spend and up to what</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr"/>
@@ -8806,10 +8994,14 @@
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr"/>
-      <c r="E204" s="4" t="inlineStr"/>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our wallet.wallet carries the balance; take their available/held split</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr"/>
@@ -8837,10 +9029,14 @@
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr"/>
-      <c r="E205" s="4" t="inlineStr"/>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>reserves wallet money mid-order; we authorise and never record the hold</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr"/>
@@ -8868,10 +9064,14 @@
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr"/>
-      <c r="E206" s="4" t="inlineStr"/>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our wallet.wallet_transaction, same table</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr"/>
@@ -8899,10 +9099,14 @@
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr"/>
-      <c r="E207" s="4" t="inlineStr"/>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our whitelabel.config_version and the branding fields on it</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr"/>
@@ -8930,10 +9134,14 @@
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr"/>
-      <c r="E208" s="4" t="inlineStr"/>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>branded URL redirects</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr"/>
@@ -8961,10 +9169,14 @@
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr"/>
-      <c r="E209" s="4" t="inlineStr"/>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>SEO and social metadata per page</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr"/>
@@ -8992,10 +9204,14 @@
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr"/>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>an employee master; we use identity.principal and hold no HR record</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr"/>
@@ -9023,10 +9239,14 @@
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr"/>
-      <c r="E211" s="4" t="inlineStr"/>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>employment terms and contract validity</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr"/>
@@ -9054,10 +9274,14 @@
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr"/>
-      <c r="E212" s="4" t="inlineStr"/>
+      <c r="E212" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>job definitions such as Cashier or Chef</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr"/>
@@ -9085,10 +9309,14 @@
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr"/>
-      <c r="E213" s="4" t="inlineStr"/>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>entitlement, used and remaining per period</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr"/>
@@ -9116,10 +9344,14 @@
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr"/>
-      <c r="E214" s="4" t="inlineStr"/>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>leave categories</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr"/>
@@ -9147,10 +9379,14 @@
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr"/>
+      <c r="E215" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr"/>
@@ -9178,10 +9414,14 @@
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr"/>
-      <c r="E216" s="4" t="inlineStr"/>
+      <c r="E216" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr"/>
@@ -9209,10 +9449,14 @@
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr"/>
-      <c r="E217" s="4" t="inlineStr"/>
+      <c r="E217" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr"/>
@@ -9240,10 +9484,14 @@
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr"/>
-      <c r="E218" s="4" t="inlineStr"/>
+      <c r="E218" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr"/>
@@ -9271,10 +9519,14 @@
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr"/>
-      <c r="E219" s="4" t="inlineStr"/>
+      <c r="E219" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
@@ -9302,10 +9554,14 @@
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr"/>
-      <c r="E220" s="4" t="inlineStr"/>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our workforce.rota_assignment</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr"/>
@@ -9333,10 +9589,14 @@
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr"/>
-      <c r="E221" s="4" t="inlineStr"/>
+      <c r="E221" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr"/>
@@ -9364,10 +9624,14 @@
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr"/>
-      <c r="E222" s="4" t="inlineStr"/>
+      <c r="E222" s="12" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr"/>
@@ -9395,10 +9659,14 @@
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr"/>
-      <c r="E223" s="4" t="inlineStr"/>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>assigns an employee to a job and a location</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr"/>
@@ -9426,10 +9694,14 @@
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="4" t="inlineStr"/>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>no candidate and not flagged</t>
+          <t>our workforce.attendance</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr"/>
@@ -9453,7 +9725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9475,7 +9747,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>82 decided, 141 open. Verdicts live in handoff/merge-verdicts.json; this sheet is generated from them.</t>
+          <t>151 decided, 72 open. Verdicts live in handoff/merge-verdicts.json; this sheet is generated from them.</t>
         </is>
       </c>
     </row>
@@ -9528,11 +9800,11 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>DECLINE</t>
+          <t>ADDITIVE</t>
         </is>
       </c>
       <c r="G5" s="16" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -9552,11 +9824,11 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>ADDITIVE</t>
+          <t>DECLINE</t>
         </is>
       </c>
       <c r="G6" s="16" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -9576,11 +9848,11 @@
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>COLLISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="G7" s="16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -9600,11 +9872,11 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>KEEP OURS</t>
+          <t>COLLISION</t>
         </is>
       </c>
       <c r="G8" s="16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -9624,11 +9896,11 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>NO MATCH</t>
+          <t>KEEP OURS</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -9648,11 +9920,11 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>TAKE THEIRS</t>
+          <t>PLACEMENT</t>
         </is>
       </c>
       <c r="G10" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -9672,7 +9944,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>NO MATCH</t>
         </is>
       </c>
       <c r="G11" s="16" t="n">
@@ -9696,11 +9968,11 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>EITHER</t>
+          <t>TAKE THEIRS</t>
         </is>
       </c>
       <c r="G12" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -9713,48 +9985,48 @@
         <v>69</v>
       </c>
       <c r="C13" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
-        <v>69</v>
-      </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>TAKE BODY</t>
+          <t>SPLIT</t>
         </is>
       </c>
       <c r="G13" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="16" t="n">
         <v>223</v>
       </c>
-      <c r="C14" s="17" t="n">
-        <v>82</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>141</v>
+      <c r="C14" s="16" t="n">
+        <v>151</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>72</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>SPLIT</t>
+          <t>EITHER</t>
         </is>
       </c>
       <c r="G14" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>RECLASSIFY</t>
+          <t>TAKE BODY</t>
         </is>
       </c>
       <c r="G15" s="16" t="n">
@@ -9764,20 +10036,30 @@
     <row r="16">
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>TAKE EITHER</t>
+          <t>RECLASSIFY</t>
         </is>
       </c>
       <c r="G16" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>PLACEMENT</t>
+          <t>TAKE EITHER</t>
         </is>
       </c>
       <c r="G17" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n">
         <v>1</v>
       </c>
     </row>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -5704,34 +5704,34 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>resources.rental_agreement</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores the operational rental lifecycle for a customer after booking/order confirmation, including planned and actual handover/return times.</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>our rental.booking carries order_id, status, from/to, checked_out_at, due_back_at and returned_at — planned and actual handover, exactly their purpose line</t>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>reversed. We hold rental.agreement_rules and rental.agreement_signature and NO agreement: the signature references participant_id plus an agreement_version string, so it signs a version number rather than a document, and rental.participant carries no booking reference at all. Their rental_agreement is the record both of ours are missing. Take it into rental; rental.booking keeps the commercial reservation and the agreement carries the operational contract, which is the split our own two tables already imply</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>TAKE BODY</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>our rental.equipment_assignment has asset_id, serial_number, assigned_at and returned_at, so partial returns already work. Take their per-item status (missing, damaged) and the quantity path for items that are not serialised</t>
+          <t>with the agreement taken, their item is the line on the contract and our rental.equipment_assignment is how a physical asset is attached to a line. Keep both roles, one table: their per-item status and quantity path for non-serialised items, our asset_id, serial_number, scanned_code and returned_at</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPLIT</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -9193,22 +9193,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Needs a choice</t>
+          <t>We accept</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MERGE</t>
+          <t>SPLIT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>We accept</t>
+          <t>Needs a choice</t>
         </is>
       </c>
     </row>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$224</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$F$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -744,34 +744,34 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>access.entry_rule</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Defines when, where, and how an entitlement may be used for entry or re-entry.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>our access.admission_rules, 37 points. Theirs is singular and ours is plural, which is our convention problem, not a rename. Their accepted entry_rule_point becomes admission_rule_point</t>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>was declined on 37 points. On the rubric it is a coin toss held hostage by our own undecided singular/plural convention: theirs is singular and pairs with the entry_rule_point we accepted, ours carries the domain word. Settle the convention, then this answers itself</t>
         </is>
       </c>
     </row>
@@ -936,34 +936,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>ai.activity</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Stores usage, cost, outcome, and trace information for any AI request, including non-chat calls.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>ai.interaction, 57 change points. "including non-chat calls" is the argument for activity, but an interaction with a system is not a chat</t>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>reversed. 57 change points is an effort argument, not a quality one, and on readability their purpose line settles it: "any AI request, including non-chat calls". An interaction reads as a conversation and most of these rows are not one</t>
         </is>
       </c>
     </row>
@@ -4840,34 +4840,34 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>orders.payment_method_config</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>NEW TABLE. Configures where a payment method is enabled, including scope, channel and currency.</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>our payments.method already holds currencies[], channels[], venue_ids[], scope_path and min/max. Theirs normalises that into a row per method x scope; ours is the ADR-0018 config-scope pattern used by 58 other scopes. Same information, our shape</t>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>reversed on the rubric. Ours is currencies[], channels[], venue_ids[] on payments.method. Optimised access: "which methods are live at this venue, in AED, on web" is an array containment scan, not an index lookup. DB strain: enabling one method at one venue rewrites the whole row and every array on it. Maintainability: adding a venue to 40 methods is 40 row rewrites against 40 inserts. We already took entry_rule_point, menu_item_modifier, seat_block_item and plan_benefit for this same reason</t>
         </is>
       </c>
     </row>
@@ -5224,34 +5224,34 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>platform.scope</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>Needs a choice</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>Stores the tenant hierarchy and links hierarchy nodes to business records owned by other services.</t>
         </is>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>our platform.org_unit. Their name is arguably better - it matches the scope_path column 58 of our configs address - but org_unit carries 91 declared foreign keys. The same cost that decides the venue schema</t>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>was declined on 91 foreign keys, which is cost. On the rubric their name is better -- scope is the word 58 of our config profiles already address by, org_unit is generic ERP. It is the venue-schema decision in a second place and belongs inside it, not settled separately on effort</t>
         </is>
       </c>
     </row>
@@ -5352,34 +5352,34 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>platform.tier_module</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>additive-declared</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>NEW TABLE. Defines which TICVAI technical modules are commercially included in a subscription tier.</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>our subscription.module_listing.included_in_tiers[] holds it as an array on the module. Feeds the module-enablement question — we have three homes for this idea</t>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>reversed on the rubric. Ours is subscription.module_listing.included_in_tiers[]. "Which modules are in PRO" scans every module row; the join table is one indexed read. Same argument as payment_method_config, and it belongs in subscription</t>
         </is>
       </c>
     </row>
@@ -6600,34 +6600,34 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>venuemap.route</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>We decline</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>DECLINE</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>EITHER</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>rename-strong</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Stores a navigable connection between two points on a venue map.</t>
         </is>
       </c>
-      <c r="F192" s="5" t="inlineStr">
-        <is>
-          <t>our venuemap.path. Both oversell it — their purpose is "a connection between two points", which is an edge; not worth a rename to find out</t>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>was declined as not worth the rename, which is a cost dodge. Their purpose is "a navigable connection between two points", which is an edge -- route and path both oversell it and neither is better. The right name is probably segment or link; concede theirs if they care</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8321,7 +8321,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>platform.subscription_tier</t>
+          <t>platform.scope</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>COLLISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -8341,19 +8341,19 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>NEW TABLE. Defines TICVAI commercial subscription tiers/packages such as BASIC, PRO, or ENTERPRISE.</t>
+          <t>Stores the tenant hierarchy and links hierarchy nodes to business records owned by other services.</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>subscription domain; ours is control.subscription_plan with cell_tier, base_price and version</t>
+          <t>was declined on 91 foreign keys, which is cost. On the rubric their name is better -- scope is the word 58 of our config profiles already address by, org_unit is generic ERP. It is the venue-schema decision in a second place and belongs inside it, not settled separately on effort</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>platform.tenant_subscription</t>
+          <t>platform.subscription_tier</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -8368,24 +8368,24 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>rename-review</t>
+          <t>rename-ambiguous</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>NEW TABLE. Stores the commercial subscription/licensing package currently assigned to a tenant.</t>
+          <t>NEW TABLE. Defines TICVAI commercial subscription tiers/packages such as BASIC, PRO, or ENTERPRISE.</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>subscription domain; ours is control.subscription</t>
+          <t>subscription domain; ours is control.subscription_plan with cell_tier, base_price and version</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>pricing.dynamic_price_action</t>
+          <t>platform.tenant_subscription</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -8395,29 +8395,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>COLLISION</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>additive-undeclared</t>
+          <t>rename-review</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Configurable dynamic pricing component for dynamic price action.</t>
+          <t>NEW TABLE. Stores the commercial subscription/licensing package currently assigned to a tenant.</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
+          <t>subscription domain; ours is control.subscription</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>pricing.dynamic_price_condition</t>
+          <t>pricing.dynamic_price_action</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Configurable dynamic pricing component for dynamic price rule condition.</t>
+          <t>Configurable dynamic pricing component for dynamic price action.</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8449,7 +8449,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>pricing.dynamic_price_rule</t>
+          <t>pricing.dynamic_price_condition</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Configurable dynamic pricing component for dynamic price rule.</t>
+          <t>Configurable dynamic pricing component for dynamic price rule condition.</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -8481,7 +8481,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>resources.rental_product_mapping</t>
+          <t>pricing.dynamic_price_rule</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -8491,29 +8491,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>COLLISION</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>rename-review</t>
+          <t>additive-undeclared</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>NEW TABLE. Maps a Catalogue rental product to the physical resource pool or quantity-based Inventory item used to fulfil it.</t>
+          <t>Configurable dynamic pricing component for dynamic price rule.</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>rental domain; ours is rental.equipment_assignment</t>
+          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>sync.guest_link</t>
+          <t>resources.rental_product_mapping</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -8523,29 +8523,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>COLLISION</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>rename-review</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Stores the pseudonymous link used to recognize the same guest across Cells without transferring the guest's full identity.</t>
+          <t>NEW TABLE. Maps a Catalogue rental product to the physical resource pool or quantity-based Inventory item used to fulfil it.</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>which schema owns cross-cell guest linking, sync or platform</t>
+          <t>rental domain; ours is rental.equipment_assignment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>venue.department</t>
+          <t>sync.guest_link</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>additive-undeclared</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Stores operational departments within a venue such as F&amp;B, Box Office, Parking, Security, or Retail.</t>
+          <t>Stores the pseudonymous link used to recognize the same guest across Cells without transferring the guest's full identity.</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>the venue schema question, with outlet, space and zone</t>
+          <t>which schema owns cross-cell guest linking, sync or platform</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>venue.outlet</t>
+          <t>venue.department</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -8592,24 +8592,24 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>additive-undeclared</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Stores physical selling or service outlets such as F&amp;B counters, retail shops, box offices, or parking booths.</t>
+          <t>Stores operational departments within a venue such as F&amp;B, Box Office, Parking, Security, or Retail.</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>the venue schema question — an open blocker</t>
+          <t>the venue schema question, with outlet, space and zone</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>venue.space</t>
+          <t>venue.outlet</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Stores physical spaces inside a venue such as screens, halls, arenas, rooms, or parking areas.</t>
+          <t>Stores physical selling or service outlets such as F&amp;B counters, retail shops, box offices, or parking booths.</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>venue.venue</t>
+          <t>venue.space</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -8656,24 +8656,24 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>additive-undeclared</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Stores the master record for each physical venue operated by a tenant.</t>
+          <t>Stores physical spaces inside a venue such as screens, halls, arenas, rooms, or parking areas.</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>the venue schema question, with outlet, space and zone</t>
+          <t>the venue schema question — an open blocker</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>venue.zone</t>
+          <t>venue.venue</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -8688,24 +8688,24 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>placement</t>
+          <t>additive-undeclared</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Stores named operational or navigational zones inside a venue or venue space.</t>
+          <t>Stores the master record for each physical venue operated by a tenant.</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>the venue schema question — an open blocker</t>
+          <t>the venue schema question, with outlet, space and zone</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>workforce.pay_component</t>
+          <t>venue.zone</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -8720,24 +8720,24 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>additive-undeclared</t>
+          <t>placement</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Defines reusable earning and deduction components.</t>
+          <t>Stores named operational or navigational zones inside a venue or venue space.</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
+          <t>the venue schema question — an open blocker</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>workforce.payroll_employee</t>
+          <t>workforce.pay_component</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Stores calculated payroll totals for one employee in a payroll run.</t>
+          <t>Defines reusable earning and deduction components.</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -8769,7 +8769,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>workforce.payroll_line</t>
+          <t>workforce.payroll_employee</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Stores detailed earnings and deductions for an employee payroll calculation.</t>
+          <t>Stores calculated payroll totals for one employee in a payroll run.</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>workforce.payroll_run</t>
+          <t>workforce.payroll_line</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Stores a payroll processing batch for a pay period.</t>
+          <t>Stores detailed earnings and deductions for an employee payroll calculation.</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -8833,7 +8833,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>workforce.payslip</t>
+          <t>workforce.payroll_run</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Stores the finalized payslip metadata for an employee/payroll result.</t>
+          <t>Stores a payroll processing batch for a pay period.</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -8865,7 +8865,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>workforce.salary</t>
+          <t>workforce.payslip</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Stores effective-dated salary configuration for an employee.</t>
+          <t>Stores the finalized payslip metadata for an employee/payroll result.</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -8897,37 +8897,69 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>workforce.salary</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Needs a choice</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Stores effective-dated salary configuration for an employee.</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>workforce.salary_component</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Stores employee-specific salary earning/deduction component values.</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39"/>
+  <autoFilter ref="A1:F40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8972,7 +9004,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -8982,7 +9014,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -8992,7 +9024,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -9039,7 +9071,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9069,7 +9101,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -9080,30 +9112,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COLLISION</t>
+          <t>TAKE THEIRS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Needs a choice</t>
+          <t>We accept</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TAKE THEIRS</t>
+          <t>COLLISION</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>We accept</t>
+          <t>Needs a choice</t>
         </is>
       </c>
     </row>
@@ -9125,11 +9157,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TAKE BODY</t>
+          <t>EITHER</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9140,11 +9172,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EITHER</t>
+          <t>TAKE BODY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tasks'!$A$1:$F$224</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Open'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,12 +66,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1320,34 +1320,34 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>catalogue.membership_benefit</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Defines a benefit that can be included in one or more membership plans.</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>benefits are columns on entitlement_template today — fast_track_tier, can_claim_shop_and_drop, included_value. Making them rows means a new benefit stops being a schema change. Real improvement, real migration</t>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Decision 9: taken. Benefits are columns on entitlement_template today, so a new benefit is a schema change. Its 15 operations and 34 screens read 34 columns to get three</t>
         </is>
       </c>
     </row>
@@ -1384,34 +1384,34 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>catalogue.membership_program</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Defines the overall membership programme available to customers.</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>the level above the plan, which we do not have. With membership_benefit and the accepted plan_benefit this is one question: does membership become its own three-level hierarchy, or stay entitlement_template plus product?</t>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Decision 9: taken, the level above the plan. membership_plan stays as our entitlement_template plus their renewal rules</t>
         </is>
       </c>
     </row>
@@ -1480,32 +1480,32 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>catalogue.product_recommendation</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Defines product recommendations for ticketing products. One table handles UPSELL, CROSS_SELL and sellable ADD_ON relationships, including targets owned by FnB or Retail.</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>matched catalogue.variant on noise; upsell lives in promotions for us</t>
         </is>
@@ -1544,160 +1544,160 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>catalogue.rental_product_config</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores rental-specific configuration for a Catalogue product, including tracking mode and operational controls.</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.product and rental.inventory_model</t>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>our rental.inventory_model. Decision 1: rental keeps its schema. catalogue.rental_rate would put rental pricing inside the hottest table set in the system, which is the flash-sale contention argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>catalogue.rental_rate</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores time-based rental prices such as per minute, hour, day, or fixed duration block.</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.pricing_profile</t>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>our rental.pricing_profile. Decision 1: rental keeps its schema. catalogue.rental_rate would put rental pricing inside the hottest table set in the system, which is the flash-sale contention argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>catalogue.rental_requirement</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Defines customer requirements that must be satisfied before a rental can be confirmed or checked out.</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.agreement_rules</t>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>our rental.agreement_rules. Decision 1: rental keeps its schema. catalogue.rental_rate would put rental pricing inside the hottest table set in the system, which is the flash-sale contention argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>catalogue.rental_rule</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Defines reusable product-level rental rules such as duration, grace, overdue charge, cancellation, pickup/return, and deposit policy.</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.operational_rules</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>our rental.operational_rules. Decision 1: rental keeps its schema. catalogue.rental_rate would put rental pricing inside the hottest table set in the system, which is the flash-sale contention argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>catalogue.upgrade_rule</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Defines valid post-purchase upgrade paths, for example Standard Ticket to VIP Ticket, and how the upgrade amount should be calculated.</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>matched catalogue.variant on noise; we serve upgrades by operation, not a rule table</t>
         </is>
@@ -1768,64 +1768,64 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>control.channel</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>Defines sales and interaction channels such as POS, Kiosk, Web, Mobile App, and partner channels.</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>matched cell_instance on noise; a sales-channel table needs its own check</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>control.channel_item</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Controls which Ticketing, FnB or Retail items can be sold through a particular sales channel and scope.</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>matched cell_instance on noise; channel-to-item mapping</t>
         </is>
@@ -2504,66 +2504,66 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>identity.customer</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Stores customer profile information and optionally links a registered customer to a login principal.</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>a guest is marketing.guest_profile plus pii.subject; identity holds principals</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>ours is marketing.guest_profile plus pii.subject. Decision 7: identity.principal carries 134 inbound foreign keys, the most connected table in the package, and their proposal adds every guest row to the table every authentication already reads. The split is also what makes a DSAR walk one subtree</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>identity.customer_address</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Stores postal, billing, and other addresses belonging to a customer.</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>pii.subject_contact holds guest contact detail</t>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>ours is pii.subject_contact. Decision 7: identity.principal carries 134 inbound foreign keys, the most connected table in the package, and their proposal adds every guest row to the table every authentication already reads. The split is also what makes a DSAR walk one subtree</t>
         </is>
       </c>
     </row>
@@ -2760,66 +2760,66 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>identity.family</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Stores one family or household group so independently registered customers can be linked together.</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>our marketing.guest_relationship</t>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>ours is marketing.guest_relationship. Decision 7: identity.principal carries 134 inbound foreign keys, the most connected table in the package, and their proposal adds every guest row to the table every authentication already reads. The split is also what makes a DSAR walk one subtree</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>identity.family_member</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>Links each registered customer to a family and records the relationship such as spouse, child or parent.</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>our marketing.guest_relationship</t>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>ours is marketing.guest_relationship. Decision 7: identity.principal carries 134 inbound foreign keys, the most connected table in the package, and their proposal adds every guest row to the table every authentication already reads. The split is also what makes a DSAR walk one subtree</t>
         </is>
       </c>
     </row>
@@ -3816,34 +3816,34 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>marketing.data_subject_request</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Tracks formal privacy/data-subject requests such as access, deletion, correction, export or restriction.</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>duplicates our platform.dsar_request — flagged 18 September, still true</t>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>our platform.dsar_request. Decision 11: a subject-access request spans every service. Ours is TenancyService and walks guest_link; theirs would be MarketingService, which owns one of the dozen schemas a DSAR has to reach</t>
         </is>
       </c>
     </row>
@@ -4040,98 +4040,98 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>marketing.loyalty_rule</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Defines temporary bonus points, multipliers, earning rules, or rewards applied by a loyalty campaign.</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>their earning and bonus rules; ours sit inside loyalty_programme</t>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>Decision 8, reversed. loyalty_programme holds no rules - it is a header. The only rules table is marketing.loyalty_tier, which is misnamed (it holds earning triggers and multipliers, not tiers) and is referenced by nothing: 0 operations, 0 screens, 0 foreign keys. Take the rule set, retire loyalty_tier, and add a real tier table so loyalty_position.tier_code points at something</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>marketing.points_earning_rule</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Defines how customers earn loyalty points from purchases or other qualifying actions.</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>they split earning and redemption; our loyalty_programme holds both</t>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Decision 8, reversed. loyalty_programme holds no rules - it is a header. The only rules table is marketing.loyalty_tier, which is misnamed (it holds earning triggers and multipliers, not tiers) and is referenced by nothing: 0 operations, 0 screens, 0 foreign keys. Take earning, retire loyalty_tier, and add a real tier table so loyalty_position.tier_code points at something</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>marketing.points_redemption_rule</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Defines how loyalty points can be exchanged for discounts, products, or other benefits.</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>they split earning and redemption; our loyalty_programme holds both</t>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Decision 8, reversed. loyalty_programme holds no rules - it is a header. The only rules table is marketing.loyalty_tier, which is misnamed (it holds earning triggers and multipliers, not tiers) and is referenced by nothing: 0 operations, 0 screens, 0 foreign keys. Take redemption, retire loyalty_tier, and add a real tier table so loyalty_position.tier_code points at something</t>
         </is>
       </c>
     </row>
@@ -4776,66 +4776,66 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>orders.payment_gateway</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
         <is>
           <t>MODIFIED. Stores payment-provider configuration for Stripe, NI and future providers, including adapter, merchant connection, capabilities and connection health.</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.provider_connection</t>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>our payments.provider_connection. Decision 2: all five are configuration, and configuration read on every checkout should not share a schema with rows written on every sale. We move orders.payment_provider, payment_token and payment_routing into payments first</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>orders.payment_method</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores the master catalogue of payment methods supported by TICVAI.</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.method</t>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>our payments.method. Decision 2: all five are configuration, and configuration read on every checkout should not share a schema with rows written on every sale. We move orders.payment_provider, payment_token and payment_routing into payments first</t>
         </is>
       </c>
     </row>
@@ -4872,98 +4872,98 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="4" t="inlineStr">
         <is>
           <t>orders.payment_policy</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores a versioned payment policy that groups payment rules and can be submitted through the existing approval workflow before activation.</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.payment_terms</t>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>our payments.payment_terms. Decision 2: all five are configuration, and configuration read on every checkout should not share a schema with rows written on every sale. We move orders.payment_provider, payment_token and payment_routing into payments first</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>orders.payment_route</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>MODIFIED. Defines payment routing by payment-method master, channel, currency, priority and provider/fallback provider.</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.routing_rule</t>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>our payments.routing_rule, and it maps onto our duplicate orders.payment_routing as well - we collapse those two. Decision 2: all five are configuration, and configuration read on every checkout should not share a schema with rows written on every sale. We move orders.payment_provider, payment_token and payment_routing into payments first</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>orders.payment_terminal</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores payment-specific configuration for a physical terminal while reusing the existing Platform device/workstation as the hardware master.</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.terminal</t>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>our payments.terminal. Decision 2: all five are configuration, and configuration read on every checkout should not share a schema with rows written on every sale. We move orders.payment_provider, payment_token and payment_routing into payments first</t>
         </is>
       </c>
     </row>
@@ -5224,98 +5224,98 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="6" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>platform.scope</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>TAKE THEIRS</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Stores the tenant hierarchy and links hierarchy nodes to business records owned by other services.</t>
         </is>
       </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>was declined on 91 foreign keys, which is cost. On the rubric their name is better -- scope is the word 58 of our config profiles already address by, org_unit is generic ERP. It is the venue-schema decision in a second place and belongs inside it, not settled separately on effort</t>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Decision 4. Their name, our table. platform.org_unit stays as one self-referencing hierarchy - flattening it into five typed tables makes adding a level a new table - but scope is the word 58 of our configuration profiles already address by, and org_unit appears nowhere else in our language</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>platform.subscription_tier</t>
         </is>
       </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>rename-ambiguous</t>
         </is>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Defines TICVAI commercial subscription tiers/packages such as BASIC, PRO, or ENTERPRISE.</t>
         </is>
       </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>subscription domain; ours is control.subscription_plan with cell_tier, base_price and version</t>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>our control.subscription_plan. Decision 3: both move into our subscription schema, which is the same service. Theirs would put billing in TenancyService and licensing in PlatformService, so a plan lookup becomes a cross-service call</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>platform.tenant_subscription</t>
         </is>
       </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Stores the commercial subscription/licensing package currently assigned to a tenant.</t>
         </is>
       </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>subscription domain; ours is control.subscription</t>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>our control.subscription. Decision 3: both move into our subscription schema, which is the same service. Theirs would put billing in TenancyService and licensing in PlatformService, so a plan lookup becomes a cross-service call</t>
         </is>
       </c>
     </row>
@@ -5416,98 +5416,98 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="6" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>pricing.dynamic_price_action</t>
         </is>
       </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Configurable dynamic pricing component for dynamic price action.</t>
         </is>
       </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Decision 5: taken, its actions. We hold three guardrail columns on rental.pricing_profile and no engine. Assign the pricing schema to CatalogueService - it has no service owner today</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>pricing.dynamic_price_condition</t>
         </is>
       </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Configurable dynamic pricing component for dynamic price rule condition.</t>
         </is>
       </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Decision 5: taken, its conditions. We hold three guardrail columns on rental.pricing_profile and no engine. Assign the pricing schema to CatalogueService - it has no service owner today</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="6" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>pricing.dynamic_price_rule</t>
         </is>
       </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Configurable dynamic pricing component for dynamic price rule.</t>
         </is>
       </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Decision 5: taken, the rule. We hold three guardrail columns on rental.pricing_profile and no engine. Assign the pricing schema to CatalogueService - it has no service owner today</t>
         </is>
       </c>
     </row>
@@ -5832,34 +5832,34 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>resources.rental_product_mapping</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>rename-review</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
         <is>
           <t>NEW TABLE. Maps a Catalogue rental product to the physical resource pool or quantity-based Inventory item used to fulfil it.</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.equipment_assignment</t>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>our rental.product.catalogue_product_id, a column. Decision 1: rental keeps its schema. catalogue.rental_rate would put rental pricing inside the hottest table set in the system, which is the flash-sale contention argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService</t>
         </is>
       </c>
     </row>
@@ -6376,194 +6376,194 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>sync.guest_link</t>
         </is>
       </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4" t="inlineStr">
         <is>
           <t>Stores the pseudonymous link used to recognize the same guest across Cells without transferring the guest's full identity.</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
-        <is>
-          <t>which schema owns cross-cell guest linking, sync or platform</t>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Decision 10, reversed. platform.dsar_request.guest_link_id points at platform.guest_link and both are TenancyService; sync is CrossRegionService. Moving the link alone puts a DSAR fan-out across a service boundary on its hottest path. Either both go or neither does, and a DSAR is a tenancy obligation rather than a synchronisation mechanism</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>venue.department</t>
         </is>
       </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>We accept</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>ADDITIVE</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Stores operational departments within a venue such as F&amp;B, Box Office, Parking, Security, or Retail.</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question, with outlet, space and zone</t>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Decision 4. Not optional: platform.workstation.department_id references a table that does not exist</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>venue.outlet</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="4" t="inlineStr">
         <is>
           <t>Stores physical selling or service outlets such as F&amp;B counters, retail shops, box offices, or parking booths.</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Decision 4. Each is a level of the platform.scope hierarchy, which we hold as a row rather than a table</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>venue.space</t>
         </is>
       </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="4" t="inlineStr">
         <is>
           <t>Stores physical spaces inside a venue such as screens, halls, arenas, rooms, or parking areas.</t>
         </is>
       </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>Decision 4. Each is a level of the platform.scope hierarchy, which we hold as a row rather than a table</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="6" t="inlineStr">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>venue.venue</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4" t="inlineStr">
         <is>
           <t>Stores the master record for each physical venue operated by a tenant.</t>
         </is>
       </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question, with outlet, space and zone</t>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Decision 4. Each is a level of the platform.scope hierarchy, which we hold as a row rather than a table</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>venue.zone</t>
         </is>
       </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>We decline</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="4" t="inlineStr">
         <is>
           <t>Stores named operational or navigational zones inside a venue or venue space.</t>
         </is>
       </c>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Decision 4. Each is a level of the platform.scope hierarchy, which we hold as a row rather than a table</t>
         </is>
       </c>
     </row>
@@ -6664,32 +6664,32 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="8" t="inlineStr">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>wallet.account</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t>RECLASSIFY</t>
         </is>
       </c>
-      <c r="D194" s="8" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E194" s="8" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>Stores the customer stored-value wallet master. It identifies whose wallet it is, wallet type, currency, and status.</t>
         </is>
       </c>
-      <c r="F194" s="9" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>their stored-value wallet master = our wallet.wallet, not ledger.account</t>
         </is>
@@ -6952,32 +6952,32 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="8" t="inlineStr">
+      <c r="A203" s="6" t="inlineStr">
         <is>
           <t>whitelabel.menu_item</t>
         </is>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B203" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="C203" s="8" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t>RECLASSIFY</t>
         </is>
       </c>
-      <c r="D203" s="8" t="inlineStr">
+      <c r="D203" s="6" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
       </c>
-      <c r="E203" s="8" t="inlineStr">
+      <c r="E203" s="6" t="inlineStr">
         <is>
           <t>Defines branded menu and navigation links shown in web/mobile experiences.</t>
         </is>
       </c>
-      <c r="F203" s="9" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>branded nav menu, not fnb.menu_item</t>
         </is>
@@ -7304,160 +7304,160 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
+      <c r="A214" s="8" t="inlineStr">
         <is>
           <t>workforce.pay_component</t>
         </is>
       </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="B214" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C214" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D214" s="6" t="inlineStr">
+      <c r="D214" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="8" t="inlineStr">
         <is>
           <t>Defines reusable earning and deduction components.</t>
         </is>
       </c>
-      <c r="F214" s="7" t="inlineStr">
+      <c r="F214" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+      <c r="A215" s="8" t="inlineStr">
         <is>
           <t>workforce.payroll_employee</t>
         </is>
       </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
+      <c r="C215" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D215" s="6" t="inlineStr">
+      <c r="D215" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>Stores calculated payroll totals for one employee in a payroll run.</t>
         </is>
       </c>
-      <c r="F215" s="7" t="inlineStr">
+      <c r="F215" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
+      <c r="A216" s="8" t="inlineStr">
         <is>
           <t>workforce.payroll_line</t>
         </is>
       </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="B216" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
+      <c r="C216" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="D216" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="8" t="inlineStr">
         <is>
           <t>Stores detailed earnings and deductions for an employee payroll calculation.</t>
         </is>
       </c>
-      <c r="F216" s="7" t="inlineStr">
+      <c r="F216" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="6" t="inlineStr">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>workforce.payroll_run</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C217" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D217" s="6" t="inlineStr">
+      <c r="D217" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="8" t="inlineStr">
         <is>
           <t>Stores a payroll processing batch for a pay period.</t>
         </is>
       </c>
-      <c r="F217" s="7" t="inlineStr">
+      <c r="F217" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="6" t="inlineStr">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>workforce.payslip</t>
         </is>
       </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C218" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D218" s="6" t="inlineStr">
+      <c r="D218" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="8" t="inlineStr">
         <is>
           <t>Stores the finalized payslip metadata for an employee/payroll result.</t>
         </is>
       </c>
-      <c r="F218" s="7" t="inlineStr">
+      <c r="F218" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
@@ -7496,64 +7496,64 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="6" t="inlineStr">
+      <c r="A220" s="8" t="inlineStr">
         <is>
           <t>workforce.salary</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="C220" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D220" s="6" t="inlineStr">
+      <c r="D220" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="8" t="inlineStr">
         <is>
           <t>Stores effective-dated salary configuration for an employee.</t>
         </is>
       </c>
-      <c r="F220" s="7" t="inlineStr">
+      <c r="F220" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
+      <c r="A221" s="8" t="inlineStr">
         <is>
           <t>workforce.salary_component</t>
         </is>
       </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D221" s="6" t="inlineStr">
+      <c r="D221" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="8" t="inlineStr">
         <is>
           <t>Stores employee-specific salary earning/deduction component values.</t>
         </is>
       </c>
-      <c r="F221" s="7" t="inlineStr">
+      <c r="F221" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
@@ -7667,7 +7667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7711,1255 +7711,231 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.membership_benefit</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>workforce.pay_component</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>rename-ambiguous</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Defines a benefit that can be included in one or more membership plans.</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>benefits are columns on entitlement_template today — fast_track_tier, can_claim_shop_and_drop, included_value. Making them rows means a new benefit stops being a schema change. Real improvement, real migration</t>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Defines reusable earning and deduction components.</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.membership_program</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>workforce.payroll_employee</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>DECIDE</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>rename-ambiguous</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Defines the overall membership programme available to customers.</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>the level above the plan, which we do not have. With membership_benefit and the accepted plan_benefit this is one question: does membership become its own three-level hierarchy, or stay entitlement_template plus product?</t>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Stores calculated payroll totals for one employee in a payroll run.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.rental_product_config</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>workforce.payroll_line</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>rename-ambiguous</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores rental-specific configuration for a Catalogue product, including tracking mode and operational controls.</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.product and rental.inventory_model</t>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Stores detailed earnings and deductions for an employee payroll calculation.</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.rental_rate</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>workforce.payroll_run</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores time-based rental prices such as per minute, hour, day, or fixed duration block.</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.pricing_profile</t>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Stores a payroll processing batch for a pay period.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.rental_requirement</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>workforce.payslip</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Defines customer requirements that must be satisfied before a rental can be confirmed or checked out.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.agreement_rules</t>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Stores the finalized payslip metadata for an employee/payroll result.</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>catalogue.rental_rule</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>workforce.salary</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Defines reusable product-level rental rules such as duration, grace, overdue charge, cancellation, pickup/return, and deposit policy.</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.operational_rules</t>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>additive-undeclared</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Stores effective-dated salary configuration for an employee.</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>identity.customer</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>workforce.salary_component</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>DECIDE</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Stores customer profile information and optionally links a registered customer to a login principal.</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>a guest is marketing.guest_profile plus pii.subject; identity holds principals</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>identity.customer_address</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Stores postal, billing, and other addresses belonging to a customer.</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>pii.subject_contact holds guest contact detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>identity.family</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Stores one family or household group so independently registered customers can be linked together.</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>our marketing.guest_relationship</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>identity.family_member</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Links each registered customer to a family and records the relationship such as spouse, child or parent.</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>our marketing.guest_relationship</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>marketing.data_subject_request</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PLACEMENT</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Tracks formal privacy/data-subject requests such as access, deletion, correction, export or restriction.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>duplicates our platform.dsar_request — flagged 18 September, still true</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>marketing.loyalty_rule</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Defines temporary bonus points, multipliers, earning rules, or rewards applied by a loyalty campaign.</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>their earning and bonus rules; ours sit inside loyalty_programme</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>marketing.points_earning_rule</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Defines how customers earn loyalty points from purchases or other qualifying actions.</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>they split earning and redemption; our loyalty_programme holds both</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>marketing.points_redemption_rule</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Defines how loyalty points can be exchanged for discounts, products, or other benefits.</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>they split earning and redemption; our loyalty_programme holds both</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>orders.payment_gateway</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>MODIFIED. Stores payment-provider configuration for Stripe, NI and future providers, including adapter, merchant connection, capabilities and connection health.</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.provider_connection</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>orders.payment_method</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores the master catalogue of payment methods supported by TICVAI.</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.method</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>orders.payment_policy</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores a versioned payment policy that groups payment rules and can be submitted through the existing approval workflow before activation.</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.payment_terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>orders.payment_route</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>MODIFIED. Defines payment routing by payment-method master, channel, currency, priority and provider/fallback provider.</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.routing_rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>orders.payment_terminal</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores payment-specific configuration for a physical terminal while reusing the existing Platform device/workstation as the hardware master.</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>payments domain; ours is payments.terminal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>platform.scope</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>rename-ambiguous</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Stores the tenant hierarchy and links hierarchy nodes to business records owned by other services.</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>was declined on 91 foreign keys, which is cost. On the rubric their name is better -- scope is the word 58 of our config profiles already address by, org_unit is generic ERP. It is the venue-schema decision in a second place and belongs inside it, not settled separately on effort</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>platform.subscription_tier</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>rename-ambiguous</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Defines TICVAI commercial subscription tiers/packages such as BASIC, PRO, or ENTERPRISE.</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>subscription domain; ours is control.subscription_plan with cell_tier, base_price and version</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>platform.tenant_subscription</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Stores the commercial subscription/licensing package currently assigned to a tenant.</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>subscription domain; ours is control.subscription</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>pricing.dynamic_price_action</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Configurable dynamic pricing component for dynamic price action.</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>pricing.dynamic_price_condition</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Configurable dynamic pricing component for dynamic price rule condition.</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>pricing.dynamic_price_rule</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Configurable dynamic pricing component for dynamic price rule.</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>a pricing schema we do not have; dynamic pricing sits in catalogue and promotions for us</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>resources.rental_product_mapping</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>COLLISION</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>rename-review</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>NEW TABLE. Maps a Catalogue rental product to the physical resource pool or quantity-based Inventory item used to fulfil it.</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>rental domain; ours is rental.equipment_assignment</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>sync.guest_link</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>placement</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Stores the pseudonymous link used to recognize the same guest across Cells without transferring the guest's full identity.</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>which schema owns cross-cell guest linking, sync or platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>venue.department</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Stores operational departments within a venue such as F&amp;B, Box Office, Parking, Security, or Retail.</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question, with outlet, space and zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>venue.outlet</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>placement</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Stores physical selling or service outlets such as F&amp;B counters, retail shops, box offices, or parking booths.</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>venue.space</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>placement</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Stores physical spaces inside a venue such as screens, halls, arenas, rooms, or parking areas.</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>venue.venue</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Stores the master record for each physical venue operated by a tenant.</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question, with outlet, space and zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>venue.zone</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>placement</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Stores named operational or navigational zones inside a venue or venue space.</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>the venue schema question — an open blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>workforce.pay_component</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Defines reusable earning and deduction components.</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Stores employee-specific salary earning/deduction component values.</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>workforce.payroll_employee</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Stores calculated payroll totals for one employee in a payroll run.</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>workforce.payroll_line</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Stores detailed earnings and deductions for an employee payroll calculation.</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>workforce.payroll_run</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Stores a payroll processing batch for a pay period.</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>workforce.payslip</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Stores the finalized payslip metadata for an employee/payroll result.</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>workforce.salary</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Stores effective-dated salary configuration for an employee.</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>workforce.salary_component</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>DECIDE</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>additive-undeclared</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Stores employee-specific salary earning/deduction component values.</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>payroll — seven tables with no requirement behind them, flagged 18 September</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F40"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8970,7 +7946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9004,7 +7980,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -9014,26 +7990,26 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Needs a choice</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>39</v>
+      <c r="B6" s="8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Correction</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9071,7 +8047,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9086,7 +8062,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9097,71 +8073,71 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DECIDE</t>
+          <t>TAKE THEIRS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Needs a choice</t>
+          <t>We accept</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TAKE THEIRS</t>
+          <t>KEEP OURS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>We accept</t>
+          <t>We decline</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COLLISION</t>
+          <t>EITHER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Needs a choice</t>
+          <t>We accept</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KEEP OURS</t>
+          <t>DECIDE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>We decline</t>
+          <t>Needs a choice</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EITHER</t>
+          <t>TAKE BODY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -9172,41 +8148,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TAKE BODY</t>
+          <t>NO MATCH</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>We accept</t>
+          <t>Correction</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLACEMENT</t>
+          <t>MERGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Needs a choice</t>
+          <t>We accept</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NO MATCH</t>
+          <t>RECLASSIFY</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -9217,58 +8193,13 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MERGE</t>
+          <t>TAKE EITHER</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>We accept</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Needs a choice</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RECLASSIFY</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Correction</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TAKE EITHER</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>We accept</t>
         </is>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Our actions'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Our actions'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$F$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open'!$A$1:$F$8</definedName>
   </definedNames>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>Their name, our table: platform.scope. Take department</t>
+          <t>Their name, our table: platform.scope. Decline all five</t>
         </is>
       </c>
       <c r="D5" s="18" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
-          <t>platform.org_unit is one self-referencing hierarchy - level, parent_id, path, child_count. Their five typed tables flatten it, so adding a level becomes a new table. But scope is the word 58 of our configuration profiles already address by. And venue.department is not optional: platform.workstation.department_id references a table that does not exist.</t>
+          <t>platform.org_unit is one self-referencing hierarchy - level, parent_id, path, child_count. Their five typed tables flatten it, so adding a level becomes a new table. But scope is the word 58 of our configuration profiles already address by. All five of their tables are levels of that hierarchy: ScopeLevel enumerates tenant, brand, region, venue, department, subDepartment, workstation, outlet and subject, and ADR-0011 makes it binding.</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1547,7 +1547,7 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Venue</t>
+          <t>Rental</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -1557,85 +1557,85 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Take venue.department</t>
+          <t>Take rental_agreement; merge rental_agreement_item with rental.equipment_assignment</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>platform.workstation.department_id references a table that does not exist.</t>
+          <t>We hold agreement_rules and agreement_signature and no agreement. The signature references a participant and a version string, and rental.participant has no booking reference.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Rental</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>Defect</t>
+          <t>Duplicate</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>Take rental_agreement; merge rental_agreement_item with rental.equipment_assignment</t>
+          <t>Collapse orders.payment_routing into payments.routing_rule</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>We hold agreement_rules and agreement_signature and no agreement. The signature references a participant and a version string, and rental.participant has no booking reference.</t>
+          <t>Both are priority plus conditions deciding a provider. Their single payment_route maps onto both of ours.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Rental</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Misplacement</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>Collapse orders.payment_routing into payments.routing_rule</t>
+          <t>Move rental.category out of rental</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Both are priority plus conditions deciding a provider. Their single payment_route maps onto both of ours.</t>
+          <t>It is the asset-category master for the whole venue - maintenance.asset, maintenance_plan, inspection_template, resources.resource_category and resource_requirement all point at it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Rental</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Misplacement</t>
+          <t>Inconsistency</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>Move rental.category out of rental</t>
+          <t>Move orders.payment_provider, payment_token and payment_routing into payments</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>It is the asset-category master for the whole venue - maintenance.asset, maintenance_plan, inspection_template, resources.resource_category and resource_requirement all point at it.</t>
+          <t>We hold payments in two schemas - 6 tables in orders, 16 in payments. Config on the wrong side of our own boundary.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Subscription</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -1645,56 +1645,56 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>Move orders.payment_provider, payment_token and payment_routing into payments</t>
+          <t>Move control.subscription and control.subscription_plan into subscription</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>We hold payments in two schemas - 6 tables in orders, 16 in payments. Config on the wrong side of our own boundary.</t>
+          <t>Subscription lives in three places. control holds 51 tables and is a junk drawer.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Inconsistency</t>
+          <t>Take theirs</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Move control.subscription and control.subscription_plan into subscription</t>
+          <t>Rename platform.org_unit to platform.scope</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Subscription lives in three places. control holds 51 tables and is a junk drawer.</t>
+          <t>Their name is better: scope is the word 58 of our configuration profiles already address by. org_unit appears nowhere else in our language.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Naming</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Take theirs</t>
+          <t>Inconsistency</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>Rename platform.org_unit to platform.scope</t>
+          <t>Publish a singular-or-plural rule and apply it to ourselves first</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Their name is better: scope is the word 58 of our configuration profiles already address by. org_unit appears nowhere else in our language.</t>
+          <t>sla_policy, admission_rules, region_settings, seating_rules. We have no rule, so we cannot argue theirs. access.entry_rule and seating.seat_rule are parked on it.</t>
         </is>
       </c>
     </row>
@@ -1711,105 +1711,83 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Publish a singular-or-plural rule and apply it to ourselves first</t>
+          <t>Take fnb.order, fnb.order_line and orders.discount</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>sla_policy, admission_rules, region_settings, seating_rules. We have no rule, so we cannot argue theirs. access.entry_rule and seating.seat_rule are parked on it.</t>
+          <t>fnb.fnb_order repeats its schema - the exact fault we ask them to fix in approvals.approval_matrix.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Naming</t>
+          <t>Pricing</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Inconsistency</t>
+          <t>Ownership</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Take fnb.order, fnb.order_line and orders.discount</t>
+          <t>Assign the pricing schema to CatalogueService</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>fnb.fnb_order repeats its schema - the exact fault we ask them to fix in approvals.approval_matrix.</t>
+          <t>It has no service owner. Leaving a schema unowned is how the last fifty unowned tables happened.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Arrays</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Ownership</t>
+          <t>Package-wide</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Assign the pricing schema to CatalogueService</t>
+          <t>Review the 140 tables carrying an array column that encodes a relationship</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>It has no service owner. Leaving a schema unowned is how the last fifty unowned tables happened.</t>
+          <t>Their workbook normalised six and we took all six. access.admission_rules.allowed_access_point_ids is the proof - their entry_rule_point IS that array as a table. The other 134 are the same decision, unreviewed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Arrays</t>
+          <t>Tooling</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Package-wide</t>
+          <t>Defect</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>Review the 140 tables carrying an array column that encodes a relationship</t>
+          <t>Fix the *_asset_id convention rule in derive-relationships.py</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>Their workbook normalised six and we took all six. access.admission_rules.allowed_access_point_ids is the proof - their entry_rule_point IS that array as a table. The other 134 are the same decision, unreviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Tooling</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Defect</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Fix the *_asset_id convention rule in derive-relationships.py</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
           <t>Five of the twelve rental-to-maintenance edges are icons, images, a PDF and two signature scans matched to maintenance.asset. They belong to assets.media_asset.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D15"/>
+  <autoFilter ref="A1:D14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7752,34 +7730,34 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="20" t="inlineStr">
+      <c r="A186" s="22" t="inlineStr">
         <is>
           <t>venue.department</t>
         </is>
       </c>
-      <c r="B186" s="20" t="inlineStr">
-        <is>
-          <t>We take theirs</t>
-        </is>
-      </c>
-      <c r="C186" s="20" t="inlineStr">
-        <is>
-          <t>ADDITIVE</t>
-        </is>
-      </c>
-      <c r="D186" s="21" t="inlineStr">
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>We keep ours</t>
+        </is>
+      </c>
+      <c r="C186" s="22" t="inlineStr">
+        <is>
+          <t>DECLINE</t>
+        </is>
+      </c>
+      <c r="D186" s="23" t="inlineStr">
         <is>
           <t>additive-undeclared</t>
         </is>
       </c>
-      <c r="E186" s="21" t="inlineStr">
+      <c r="E186" s="23" t="inlineStr">
         <is>
           <t>Stores operational departments within a venue such as F&amp;B, Box Office, Parking, Security, or Retail.</t>
         </is>
       </c>
-      <c r="F186" s="21" t="inlineStr">
-        <is>
-          <t>Decision 4. Not optional: platform.workstation.department_id references a table that does not exist</t>
+      <c r="F186" s="23" t="inlineStr">
+        <is>
+          <t>corrected. department is one of nine ScopeLevel values in contracts/shared/common.yaml - tenant, brand, region, venue, department, subDepartment, workstation, outlet, subject - and ADR-0011 makes the hierarchy binding. platform.org_unit holds a department as a row with level=department, and platform.workstation.department_id points at it. We had this as a dangling reference and a gap; it is neither. Their five venue tables are five of our nine levels flattened into tables, which is the decision-4 argument applied to the one table we had conceded</t>
         </is>
       </c>
     </row>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Our actions'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$F$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open'!$A$1:$F$1</definedName>
@@ -901,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="I2" s="18" t="inlineStr">
         <is>
-          <t>catalogue.rental_rate puts rental pricing inside the hottest table set in the system - the flash-sale argument that gave F&amp;B and Retail their own price tables. Their layout also splits rental across CatalogueService and VenueOpsService. But we hold agreement_rules and agreement_signature and NO agreement: the signature signs a version string, and rental.participant has no booking reference at all.</t>
+          <t>catalogue.rental_rate puts rental pricing inside the hottest table set in the system - catalogue.product alone is read by twelve contracts across 40 operations. Their layout also splits rental across CatalogueService and VenueOpsService. But we hold agreement_rules and agreement_signature and NO agreement: the signature signs a version string, and rental.participant has no booking reference at all.</t>
         </is>
       </c>
     </row>
@@ -1435,8 +1435,94 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Currency on nine accepted tables</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>Seven genuinely differ, two are copies</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>ADR-0018 resolves currency from the region and does not store it, so a generated schema putting a currency column on anything holding money is supplying the conventional thing and missing the specific one. Seven of the nine are exempt for a real reason; two are copies of a fact that cannot differ and are marked not-persisted. It amended ADR-0018: a venue may set its own currency and it freezes at the first trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>The F&amp;B and Retail catalogue</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>COLLAPSE into catalogue.* - keep six columns</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>We took their ten product/category/variant/price/price_list tables on a DB-strain argument and then measured it: catalogue.product has 40 operations across twelve contracts and all ten of the new tables have zero. No retail operation reads catalogue.product at all. A split that relieves contention needs the READS moved, not the tables added - we paid the whole maintenance cost and got none of the isolation. Three to one on the rubric, and the one criterion the split wins is unexercised; x-ticvai-read-routing: analytical already exists for real contention. Six of their columns stay, including product.categoryId - catalogue.product_category had two operations since 20 August and nothing could be filed under it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decisions'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Our actions'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$F$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open'!$A$1:$F$1</definedName>
@@ -901,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1521,8 +1521,94 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>The tier table decision 8 promised</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>marketing.programme_tier - and keep the cache</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Decision 8 said retire loyalty_tier and add a real tier table; the retire happened and the add did not, so loyalty_position carried tierCode and tierName as denormalised strings and pointsToNextTier was computed from a threshold that lived nowhere. The name was the part that needed deciding: marketing.loyalty_tier is spent - schema-history declares it renamed to points_earning_rule - and marketing.tier would repeat the subscription.plan collision. The answer is BOTH the table and the cache: maintainability and readability want the table, optimised access and cross-cell want the strings, because reading a definition to render a badge would be a cross-cell call to print a word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Inspection answers</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>maintenance.inspection_item</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>theirs</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>ours</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>SubmitInspectionRequest.responses[] has always taken a key, a value, a pass flag, a note and attachments, tagged 'none - request only', and the only persistence ever claimed was maintenance.inspection_response, which does not exist. The template held the questions, the inspection held failedItemCount, and which check failed was accepted over the wire and dropped - on a record that takes an asset out of service. Items go on InspectionResult, the detail response, not on Inspection, the list row, and the counts stay because listInspections returns it in a list.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
+++ b/ticvai/handoff/TICVAI_Schema_Merge_Tasks.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>payroll — a scope question, not a schema one</t>
+          <t>nothing is outstanding; payroll closed on their own sources (see Decision 6)</t>
         </is>
       </c>
     </row>
